--- a/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
+++ b/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
@@ -730,16 +730,16 @@
         <v>27.3</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>13213185</v>
+        <v>12948348</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>30000</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>13183185</v>
+        <v>12918348</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -804,16 +804,16 @@
         <v>27.3</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>41868550</v>
+        <v>41603712</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>571000</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>41297550</v>
+        <v>41032712</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>1513</v>
+        <v>1503</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
@@ -836,14 +836,14 @@
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>— Разница между продажей и ломом — 26.3 млн руб. Лом дает 13.2 млн за несколько дней, продажа 39.5 млн за месяцы и с отсрочкой платежа. Это и есть цена нашей работы: инвентаризация, контейнер, хранение, переговоры и ожидание.</t>
+          <t>— Разница между продажей и ломом — 26.6 млн руб. Лом дает 12.9 млн за несколько дней, продажа 39.5 млн за месяцы и с отсрочкой платежа. Это и есть цена нашей работы: инвентаризация, контейнер, хранение, переговоры и ожидание.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>— В пересчете на килограмм: лом дает 483 руб, продажа 1447 руб. Разница 983 руб с килограмма.</t>
+          <t>— В пересчете на килограмм: лом дает 473 руб, продажа 1447 руб. Разница 993 руб с килограмма.</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>— Лом считаем по латуни. Если материал разделить и бронзу сдать по 600, лом вырастет до 15.8 млн. Это еще один довод проставить материал в учете.</t>
+          <t>— Лом считаем по латуни. Если материал разделить и бронзу сдать по 600, лом вырастет до 15.3 млн. Это еще один довод проставить материал в учете.</t>
         </is>
       </c>
     </row>
@@ -967,22 +967,22 @@
         <v>10703</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>5138184</v>
+        <v>4882864</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>12761000</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>1192</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>712</v>
+        <v>736</v>
       </c>
     </row>
     <row r="6">
@@ -1618,7 +1618,7 @@
         <v>363</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>181400</v>
+        <v>171882</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>0</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="H26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>-500</v>
+        <v>-474</v>
       </c>
     </row>
   </sheetData>
@@ -1825,7 +1825,7 @@
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="F7" s="26" t="n">
@@ -1835,7 +1835,7 @@
         <v>520</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>260000</v>
+        <v>4680</v>
       </c>
       <c r="I7" s="26" t="n"/>
       <c r="J7" s="27" t="n"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F12" s="26" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F15" s="26" t="n">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F32" s="26" t="n">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="F38" s="26" t="n">
@@ -2996,7 +2996,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="26" t="n">
-        <v>4700</v>
+        <v>893</v>
       </c>
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="27" t="n"/>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="F43" s="26" t="n">
@@ -3187,7 +3187,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="26" t="n">
-        <v>4350</v>
+        <v>826</v>
       </c>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="27" t="n"/>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="F52" s="26" t="n">
@@ -3532,7 +3532,7 @@
         <v>5</v>
       </c>
       <c r="H52" s="26" t="n">
-        <v>2700</v>
+        <v>513</v>
       </c>
       <c r="I52" s="26" t="n"/>
       <c r="J52" s="27" t="n"/>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F56" s="26" t="n">

--- a/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
+++ b/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="По группам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Кандидаты в лом" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По группам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кандидаты в лом" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Весь перечень на отгрузку — 286 позиций, 27.30 т. Лом считаем по латуни 500 руб за кг: материал в учете почти нигде не разделен, по бронзе граница выше.</t>
+          <t>Весь перечень на отгрузку — 286 позиций, 28.99 т. Лом считаем по латуни 500 руб за кг: материал в учете почти нигде не разделен, по бронзе граница выше.</t>
         </is>
       </c>
     </row>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>27.3</v>
+        <v>28.99</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>12948348</v>
+        <v>13775052</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>30000</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>12918348</v>
+        <v>13745052</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>27.3</v>
+        <v>28.99</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>40043750</v>
@@ -776,7 +776,7 @@
         <v>39502750</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1447</v>
+        <v>1363</v>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>27.3</v>
+        <v>28.99</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>41603712</v>
+        <v>41532212</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>571000</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>41032712</v>
+        <v>40961212</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>1503</v>
+        <v>1413</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
@@ -836,14 +836,14 @@
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>— Разница между продажей и ломом — 26.6 млн руб. Лом дает 12.9 млн за несколько дней, продажа 39.5 млн за месяцы и с отсрочкой платежа. Это и есть цена нашей работы: инвентаризация, контейнер, хранение, переговоры и ожидание.</t>
+          <t>— Разница между продажей и ломом — 25.8 млн руб. Лом дает 13.7 млн за несколько дней, продажа 39.5 млн за месяцы и с отсрочкой платежа. Это и есть цена нашей работы: инвентаризация, контейнер, хранение, переговоры и ожидание.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>— В пересчете на килограмм: лом дает 473 руб, продажа 1447 руб. Разница 993 руб с килограмма.</t>
+          <t>— В пересчете на килограмм: лом дает 474 руб, продажа 1363 руб. Разница 906 руб с килограмма.</t>
         </is>
       </c>
     </row>
@@ -857,14 +857,14 @@
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>— Смешанный сценарий почти не отличается от продажи: позиций около лома всего 66  и весят они 4 929 кг. Отдельно возиться с ними смысла нет  но и везти через всю страну незачем.</t>
+          <t>— Смешанный сценарий почти не отличается от продажи: позиций около лома всего 66  и весят они 4 786 кг. Отдельно возиться с ними смысла нет  но и везти через всю страну незачем.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>— Лом считаем по латуни. Если материал разделить и бронзу сдать по 600, лом вырастет до 15.3 млн. Это еще один довод проставить материал в учете.</t>
+          <t>— Лом считаем по латуни. Если материал разделить и бронзу сдать по 600, лом вырастет до 16.3 млн. Это еще один довод проставить материал в учете.</t>
         </is>
       </c>
     </row>
@@ -964,25 +964,25 @@
         <v>24</v>
       </c>
       <c r="C5" s="21" t="n">
-        <v>10703</v>
+        <v>12294</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>4882864</v>
+        <v>5659878</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>12761000</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>1192</v>
+        <v>1038</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>736</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6">
@@ -1026,25 +1026,25 @@
         <v>34</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>4199</v>
+        <v>4257</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>2029452</v>
+        <v>2059988</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>6826600</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>1626</v>
+        <v>1604</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>1143</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8">
@@ -1057,25 +1057,25 @@
         <v>9</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>1828</v>
+        <v>1834</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>913911</v>
+        <v>917000</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>2338000</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G8" s="21" t="n">
         <v>500</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="9">
@@ -1088,10 +1088,10 @@
         <v>27</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>1748</v>
+        <v>1788</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>868261</v>
+        <v>884380</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>2087200</v>
@@ -1100,13 +1100,13 @@
         <v>2.4</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>1194</v>
+        <v>1167</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>698</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10">
@@ -1277,7 +1277,7 @@
         <v>112</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>56003</v>
+        <v>55950</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>405000</v>
@@ -1289,10 +1289,10 @@
         <v>500</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>3616</v>
+        <v>3619</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>3116</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="16">
@@ -1673,7 +1673,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>66 позиций  4 929 кг. Сюда попадает то  где наша цена ниже 1.5 лома  и то  где цены нет вообще. Везти такое через всю страну и потом хранить в Петербурге смысла мало.</t>
+          <t>66 позиций  4 786 кг. Сюда попадает то  где наша цена ниже 1.5 лома  и то  где цены нет вообще. Везти такое через всю страну и потом хранить в Петербурге смысла мало.</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr"/>
       <c r="D8" s="24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="F8" s="26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>247500</v>
+        <v>231200</v>
       </c>
       <c r="I8" s="26" t="n"/>
       <c r="J8" s="27" t="n"/>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr"/>
       <c r="D9" s="24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="F9" s="26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>462</v>
+        <v>352</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>231200</v>
+        <v>176000</v>
       </c>
       <c r="I9" s="26" t="n"/>
       <c r="J9" s="27" t="n"/>

--- a/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
+++ b/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
@@ -173,8 +173,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Весь перечень на отгрузку — 286 позиций, 28.99 т. Лом считаем по латуни 500 руб за кг: материал в учете почти нигде не разделен, по бронзе граница выше.</t>
+          <t>Весь перечень на отгрузку — 286 позиций, 28.99 т. Лом считаем по бронзе 745 руб за кг: по ней же собственник назначил закупочную цену, лом на 2,5.</t>
         </is>
       </c>
     </row>
@@ -593,30 +593,30 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Латунь, руб за кг</t>
+          <t>Бронза, руб за кг</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>по ней и считаем</t>
+          <t>по ней и считаем, класс «бронза/латунь» идет сюда</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Бронза, руб за кг</t>
+          <t>Латунь, руб за кг</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>600</v>
+        <v>635</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>верхняя граница лома</t>
+          <t>нижняя граница, если материал разделить</t>
         </is>
       </c>
     </row>
@@ -627,244 +627,266 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Довезти до приемки во Владивостоке</t>
+          <t>Закупочная цена, лом на</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30000</v>
+        <v>2.5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>своя машина по городу, несколько рейсов</t>
+          <t>договоренность с Антоном от 25.10.2026: по бронзе 1 862.50 руб за кг</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Довезти до приемки во Владивостоке</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>своя машина по городу, несколько рейсов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Отгрузка в Петербург, сорокафутовый</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>541000</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>контейнер, авто на обоих концах, погрузка</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Три сценария</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Сценарий</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Что уходит</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Вес, т</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Выручка, руб</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Расходы, руб</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>На руки, руб</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Руб за кг</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Срок</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Когда деньги</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Сдать все в лом</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>286 позиций целиком</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C14" s="9" t="n">
         <v>28.99</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>13775052</v>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="D14" s="10" t="n">
+        <v>20507504</v>
+      </c>
+      <c r="E14" s="10" t="n">
         <v>30000</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>13745052</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>474</v>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="F14" s="10" t="n">
+        <v>20477504</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>706</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>несколько дней</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>сразу, по факту сдачи</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Продать все по позициям</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>286 позиций в Петербург</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C15" s="13" t="n">
         <v>28.99</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D15" s="14" t="n">
         <v>40043750</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E15" s="14" t="n">
         <v>541000</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F15" s="14" t="n">
         <v>39502750</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G15" s="14" t="n">
         <v>1363</v>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>месяцы</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>по мере реализации, отсрочка по договору</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Смешанный: продать дорогое, сдать остальное</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>продать 220, сдать 66</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="n">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>продать 197, сдать 89</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
         <v>28.99</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <v>41532212</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="D16" s="18" t="n">
+        <v>40912453</v>
+      </c>
+      <c r="E16" s="18" t="n">
         <v>571000</v>
       </c>
-      <c r="F15" s="18" t="n">
-        <v>40961212</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>1413</v>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="F16" s="18" t="n">
+        <v>40341453</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1391</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>месяцы, но груза меньше</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>часть сразу, часть по реализации</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Что показывает сравнение</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>— Разница между продажей и ломом — 25.8 млн руб. Лом дает 13.7 млн за несколько дней, продажа 39.5 млн за месяцы и с отсрочкой платежа. Это и есть цена нашей работы: инвентаризация, контейнер, хранение, переговоры и ожидание.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>— В пересчете на килограмм: лом дает 474 руб, продажа 1363 руб. Разница 906 руб с килограмма.</t>
+          <t>— Разница между продажей и ломом — 19.0 млн руб. Лом дает 20.5 млн за несколько дней, продажа 39.5 млн за месяцы и с отсрочкой платежа. Это и есть цена нашей работы: инвентаризация, контейнер, хранение, переговоры и ожидание.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>— Доставка в Петербург на этом фоне мелочь: 541 000 руб — 1.4% выручки от продажи. Экономить на контейнере бессмысленно  а вот сдать в лом вместо продажи — потерять две трети денег.</t>
+          <t>— В пересчете на килограмм: лом дает 706 руб, продажа 1363 руб. Разница 674 руб с килограмма.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>— Смешанный сценарий почти не отличается от продажи: позиций около лома всего 66  и весят они 4 786 кг. Отдельно возиться с ними смысла нет  но и везти через всю страну незачем.</t>
+          <t>— Доставка в Петербург на этом фоне мелочь: 541 000 руб — 1.4% выручки от продажи. Экономить на контейнере бессмысленно  а вот сдать в лом вместо продажи — потерять 48% денег.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>— Лом считаем по латуни. Если материал разделить и бронзу сдать по 600, лом вырастет до 16.3 млн. Это еще один довод проставить материал в учете.</t>
+          <t>— Смешанный сценарий почти не отличается от продажи: позиций около лома всего 89  и весят они 11 383 кг. Отдельно возиться с ними смысла нет  но и везти через всю страну незачем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>— Лом считаем по бронзе 745 руб за кг. Если часть окажется латунью по 635, лом просядет до 17.3 млн. Это еще один довод проставить материал в учете.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>— Цена по договору — это тот же лом  умноженный на 2.5: бронза 745 на 2.5 дает 1 862.50 руб за кг. То есть продажа по спецификации и есть лом с коэффициентом  и запас над приемкой зашит в саму цену.</t>
         </is>
       </c>
     </row>
@@ -967,22 +989,22 @@
         <v>12294</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>5659878</v>
+        <v>8438764</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>12761000</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>460</v>
+        <v>686</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>1038</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>578</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6">
@@ -998,22 +1020,22 @@
         <v>2449</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>1222135</v>
+        <v>1821007</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>8483500</v>
       </c>
-      <c r="F6" s="22" t="n">
-        <v>6.9</v>
+      <c r="F6" s="23" t="n">
+        <v>4.7</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>499</v>
+        <v>744</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>3464</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>2965</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="7">
@@ -1029,22 +1051,22 @@
         <v>4257</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>2059988</v>
+        <v>3079242</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>6826600</v>
       </c>
-      <c r="F7" s="22" t="n">
-        <v>3.3</v>
+      <c r="F7" s="23" t="n">
+        <v>2.2</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>484</v>
+        <v>723</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>1604</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>1120</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8">
@@ -1060,22 +1082,22 @@
         <v>1834</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>917000</v>
+        <v>1366330</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>2338000</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>1275</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>775</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9">
@@ -1091,22 +1113,22 @@
         <v>1788</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>884380</v>
+        <v>1317838</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>2087200</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>495</v>
+        <v>737</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>1167</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>673</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10">
@@ -1122,22 +1144,22 @@
         <v>666</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>331972</v>
+        <v>494687</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>1760200</v>
       </c>
-      <c r="F10" s="22" t="n">
-        <v>5.3</v>
+      <c r="F10" s="23" t="n">
+        <v>3.6</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>498</v>
+        <v>743</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>2643</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>2144</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="11">
@@ -1153,22 +1175,22 @@
         <v>3490</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>1745100</v>
+        <v>2600199</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>1750000</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>1</v>
+      <c r="F11" s="22" t="n">
+        <v>0.7</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>501</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>1</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="12">
@@ -1184,22 +1206,22 @@
         <v>263</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>131450</v>
+        <v>195860</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>1343500</v>
       </c>
-      <c r="F12" s="22" t="n">
-        <v>10.2</v>
+      <c r="F12" s="23" t="n">
+        <v>6.9</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>5110</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>4610</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="13">
@@ -1215,22 +1237,22 @@
         <v>346</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>173250</v>
+        <v>258142</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>945000</v>
       </c>
-      <c r="F13" s="22" t="n">
-        <v>5.5</v>
+      <c r="F13" s="23" t="n">
+        <v>3.7</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>2727</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>2227</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="14">
@@ -1246,22 +1268,22 @@
         <v>110</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>54800</v>
+        <v>81652</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>415000</v>
       </c>
-      <c r="F14" s="22" t="n">
-        <v>7.6</v>
+      <c r="F14" s="23" t="n">
+        <v>5.1</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>3786</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>3286</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="15">
@@ -1277,22 +1299,22 @@
         <v>112</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>55950</v>
+        <v>83366</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>405000</v>
       </c>
-      <c r="F15" s="22" t="n">
-        <v>7.2</v>
+      <c r="F15" s="23" t="n">
+        <v>4.9</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>3619</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>3119</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="16">
@@ -1308,22 +1330,22 @@
         <v>258</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>2322</v>
+        <v>4902</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>345000</v>
       </c>
-      <c r="F16" s="22" t="n">
-        <v>148.6</v>
+      <c r="F16" s="23" t="n">
+        <v>70.40000000000001</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>1337</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>1328</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="17">
@@ -1339,22 +1361,22 @@
         <v>204</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>101775</v>
+        <v>151645</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>277500</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>1363</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>863</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1392,22 @@
         <v>100</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>49800</v>
+        <v>74202</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>100000</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>1004</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>504</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19">
@@ -1401,22 +1423,22 @@
         <v>106</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>53000</v>
+        <v>78970</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>74250</v>
       </c>
-      <c r="F19" s="23" t="n">
-        <v>1.4</v>
+      <c r="F19" s="22" t="n">
+        <v>0.9</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>700</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>200</v>
+        <v>-45</v>
       </c>
     </row>
     <row r="20">
@@ -1432,22 +1454,22 @@
         <v>33</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>293</v>
+        <v>619</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>60000</v>
       </c>
-      <c r="F20" s="22" t="n">
-        <v>204.5</v>
+      <c r="F20" s="23" t="n">
+        <v>96.90000000000001</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>1840</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>1831</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="21">
@@ -1463,22 +1485,22 @@
         <v>170</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>84827</v>
+        <v>126392</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>47000</v>
       </c>
-      <c r="F21" s="23" t="n">
-        <v>0.6</v>
+      <c r="F21" s="22" t="n">
+        <v>0.4</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>277</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>-223</v>
+        <v>-468</v>
       </c>
     </row>
     <row r="22">
@@ -1494,22 +1516,22 @@
         <v>85</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>42700</v>
+        <v>63623</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>25000</v>
       </c>
-      <c r="F22" s="23" t="n">
-        <v>0.6</v>
+      <c r="F22" s="22" t="n">
+        <v>0.4</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H22" s="21" t="n">
         <v>293</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>-207</v>
+        <v>-452</v>
       </c>
     </row>
     <row r="23">
@@ -1525,22 +1547,22 @@
         <v>9</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>4500</v>
+        <v>6705</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H23" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>-500</v>
+        <v>-745</v>
       </c>
     </row>
     <row r="24">
@@ -1556,22 +1578,22 @@
         <v>4</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>2000</v>
+        <v>2980</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>-500</v>
+        <v>-745</v>
       </c>
     </row>
     <row r="25">
@@ -1587,22 +1609,22 @@
         <v>52</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>26050</v>
+        <v>38814</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="H25" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>-500</v>
+        <v>-745</v>
       </c>
     </row>
     <row r="26">
@@ -1618,22 +1640,22 @@
         <v>363</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>171882</v>
+        <v>221566</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>474</v>
+        <v>611</v>
       </c>
       <c r="H26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>-474</v>
+        <v>-611</v>
       </c>
     </row>
   </sheetData>
@@ -1647,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1673,7 +1695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>66 позиций  4 786 кг. Сюда попадает то  где наша цена ниже 1.5 лома  и то  где цены нет вообще. Везти такое через всю страну и потом хранить в Петербурге смысла мало.</t>
+          <t>89 позиций  11 383 кг. Сюда попадает то  где наша цена ниже 1.5 лома  и то  где цены нет вообще. Везти такое через всю страну и потом хранить в Петербурге смысла мало.</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1762,12 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Клинкет Ду 300</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
       <c r="D5" s="24" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -1756,16 +1778,20 @@
         <v>13</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>751</v>
+        <v>2496</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>375700</v>
-      </c>
-      <c r="I5" s="26" t="n"/>
-      <c r="J5" s="27" t="n"/>
+        <v>1859520</v>
+      </c>
+      <c r="I5" s="26" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>1.4</v>
+      </c>
       <c r="K5" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1801,12 @@
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Клинкет Ду 200</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr"/>
       <c r="D6" s="24" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
@@ -1791,16 +1817,16 @@
         <v>15</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>714</v>
+        <v>1320</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>357000</v>
+        <v>983400</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>525000</v>
+        <v>1350000</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
@@ -1814,34 +1840,36 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>Задвижки (желтая) ок. крышек</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>544-03.046</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="n"/>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="n">
+        <v>80</v>
+      </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F7" s="26" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>520</v>
+        <v>1056</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>4680</v>
-      </c>
-      <c r="I7" s="26" t="n"/>
-      <c r="J7" s="27" t="n"/>
+        <v>786720</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>1.34</v>
+      </c>
       <c r="K7" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -1864,19 +1892,23 @@
         </is>
       </c>
       <c r="F8" s="26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>462</v>
+        <v>816</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>231200</v>
-      </c>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="27" t="n"/>
+        <v>607920</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>660000</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>1.09</v>
+      </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1918,12 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr"/>
       <c r="D9" s="24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
@@ -1899,13 +1931,13 @@
         </is>
       </c>
       <c r="F9" s="26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>352</v>
+        <v>751</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>176000</v>
+        <v>559793</v>
       </c>
       <c r="I9" s="26" t="n"/>
       <c r="J9" s="27" t="n"/>
@@ -1921,12 +1953,12 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr"/>
       <c r="D10" s="24" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
@@ -1934,19 +1966,23 @@
         </is>
       </c>
       <c r="F10" s="26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>330</v>
+        <v>714</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>165000</v>
-      </c>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="27" t="n"/>
+        <v>531930</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>525000</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>0.99</v>
+      </c>
       <c r="K10" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена ниже лома</t>
         </is>
       </c>
     </row>
@@ -1956,26 +1992,28 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr"/>
-      <c r="D11" s="24" t="n">
-        <v>100</v>
-      </c>
+          <t>Задвижки (желтая) ок. крышек</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>544-03.046</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n"/>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="F11" s="26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>280</v>
+        <v>520</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>140000</v>
+        <v>9880</v>
       </c>
       <c r="I11" s="26" t="n"/>
       <c r="J11" s="27" t="n"/>
@@ -1991,30 +2029,26 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>(541-03.218)</t>
-        </is>
-      </c>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr"/>
       <c r="D12" s="24" t="n">
         <v>80</v>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>213</v>
+        <v>462</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>106400</v>
+        <v>344488</v>
       </c>
       <c r="I12" s="26" t="n"/>
       <c r="J12" s="27" t="n"/>
@@ -2030,12 +2064,12 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr"/>
       <c r="D13" s="24" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
@@ -2043,23 +2077,19 @@
         </is>
       </c>
       <c r="F13" s="26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G13" s="26" t="n">
-        <v>135</v>
+        <v>352</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>67627</v>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>37000</v>
-      </c>
-      <c r="J13" s="28" t="n">
-        <v>0.55</v>
-      </c>
+        <v>262240</v>
+      </c>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="27" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
-          <t>цена ниже лома</t>
+          <t>цены нет</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2099,12 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr"/>
       <c r="D14" s="24" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
@@ -2082,13 +2112,13 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>55000</v>
+        <v>245850</v>
       </c>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="27" t="n"/>
@@ -2104,30 +2134,26 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>(541-03.220)</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый угловой Ду100</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr"/>
       <c r="D15" s="24" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F15" s="26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>109</v>
+        <v>280</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>54600</v>
+        <v>208600</v>
       </c>
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="27" t="n"/>
@@ -2143,26 +2169,30 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr"/>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>(541-03.218)</t>
+        </is>
+      </c>
       <c r="D16" s="24" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>53250</v>
+        <v>135128</v>
       </c>
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="27" t="n"/>
@@ -2178,7 +2208,7 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr"/>
@@ -2191,19 +2221,23 @@
         </is>
       </c>
       <c r="F17" s="26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="H17" s="26" t="n">
-        <v>35500</v>
-      </c>
-      <c r="I17" s="26" t="n"/>
-      <c r="J17" s="27" t="n"/>
+        <v>152725</v>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>175000</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>1.15</v>
+      </c>
       <c r="K17" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2213,36 +2247,36 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>521-182.110</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду150</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr"/>
       <c r="D18" s="24" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>титан</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="H18" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="27" t="n"/>
+        <v>111750</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>160000</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>1.43</v>
+      </c>
       <c r="K18" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2252,11 +2286,13 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="D19" s="24" t="n">
+        <v>125</v>
+      </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -2266,20 +2302,20 @@
         <v>1</v>
       </c>
       <c r="G19" s="26" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="H19" s="26" t="n">
-        <v>20000</v>
+        <v>100764</v>
       </c>
       <c r="I19" s="26" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>1</v>
+        <v>37000</v>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>0.37</v>
       </c>
       <c r="K19" s="24" t="inlineStr">
         <is>
-          <t>цена почти как лом</t>
+          <t>цена ниже лома</t>
         </is>
       </c>
     </row>
@@ -2289,16 +2325,12 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>554-03.905-06</t>
-        </is>
-      </c>
+          <t>Фильтр заборной воды ДУ 80</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr"/>
       <c r="D20" s="24" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
@@ -2306,13 +2338,13 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>19500</v>
+        <v>81950</v>
       </c>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="27" t="n"/>
@@ -2328,24 +2360,30 @@
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr"/>
-      <c r="D21" s="24" t="n"/>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>(541-03.220)</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="n">
+        <v>125</v>
+      </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F21" s="26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G21" s="26" t="n">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="H21" s="26" t="n">
-        <v>18450</v>
+        <v>69342</v>
       </c>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="27" t="n"/>
@@ -2361,7 +2399,7 @@
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr"/>
@@ -2377,10 +2415,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>18000</v>
+        <v>79342</v>
       </c>
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="27" t="n"/>
@@ -2396,12 +2434,12 @@
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr"/>
       <c r="D23" s="24" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
@@ -2409,19 +2447,19 @@
         </is>
       </c>
       <c r="F23" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>17000</v>
+        <v>67422</v>
       </c>
       <c r="I23" s="26" t="n">
-        <v>19500</v>
+        <v>80000</v>
       </c>
       <c r="J23" s="27" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
@@ -2435,16 +2473,12 @@
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>529-03.003</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr"/>
       <c r="D24" s="24" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
@@ -2455,16 +2489,20 @@
         <v>1</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>16850</v>
-      </c>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="27" t="n"/>
+        <v>55875</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>1.43</v>
+      </c>
       <c r="K24" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2474,30 +2512,40 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr"/>
-      <c r="D25" s="24" t="n"/>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>521-01.207</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>150</v>
+      </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F25" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>12300</v>
-      </c>
-      <c r="I25" s="26" t="n"/>
-      <c r="J25" s="27" t="n"/>
+        <v>55875</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J25" s="27" t="n">
+        <v>1.43</v>
+      </c>
       <c r="K25" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2507,16 +2555,12 @@
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру40</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>521-03.230</t>
-        </is>
-      </c>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr"/>
       <c r="D26" s="24" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
@@ -2524,13 +2568,13 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>10000</v>
+        <v>52895</v>
       </c>
       <c r="I26" s="26" t="n"/>
       <c r="J26" s="27" t="n"/>
@@ -2546,16 +2590,12 @@
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
@@ -2563,19 +2603,23 @@
         </is>
       </c>
       <c r="F27" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="H27" s="26" t="n">
-        <v>9500</v>
-      </c>
-      <c r="I27" s="26" t="n"/>
-      <c r="J27" s="27" t="n"/>
+        <v>47680</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>70000</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>1.47</v>
+      </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2585,16 +2629,12 @@
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>521-03.387</t>
-        </is>
-      </c>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="24" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
@@ -2602,19 +2642,23 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>8600</v>
-      </c>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="27" t="n"/>
+        <v>44700</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <v>1.12</v>
+      </c>
       <c r="K28" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2624,16 +2668,12 @@
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>521-35.2608-01</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr"/>
       <c r="D29" s="24" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
@@ -2641,19 +2681,23 @@
         </is>
       </c>
       <c r="F29" s="26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G29" s="26" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="H29" s="26" t="n">
-        <v>8550</v>
-      </c>
-      <c r="I29" s="26" t="n"/>
-      <c r="J29" s="27" t="n"/>
+        <v>40975</v>
+      </c>
+      <c r="I29" s="26" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J29" s="27" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2707,12 @@
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr"/>
       <c r="D30" s="24" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
@@ -2676,19 +2720,19 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>8500</v>
+        <v>35760</v>
       </c>
       <c r="I30" s="26" t="n">
-        <v>9750</v>
+        <v>48000</v>
       </c>
       <c r="J30" s="27" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="K30" s="24" t="inlineStr">
         <is>
@@ -2702,30 +2746,30 @@
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>521-35.2754</t>
+          <t>521-182.110</t>
         </is>
       </c>
       <c r="D31" s="24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>титан</t>
         </is>
       </c>
       <c r="F31" s="26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="26" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H31" s="26" t="n">
-        <v>6900</v>
+        <v>5958</v>
       </c>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="27" t="n"/>
@@ -2741,36 +2785,34 @@
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>(541-03.232)</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>25</v>
-      </c>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr"/>
+      <c r="D32" s="24" t="n"/>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G32" s="26" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H32" s="26" t="n">
-        <v>6400</v>
-      </c>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="27" t="n"/>
+        <v>29800</v>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J32" s="28" t="n">
+        <v>0.67</v>
+      </c>
       <c r="K32" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена ниже лома</t>
         </is>
       </c>
     </row>
@@ -2780,28 +2822,30 @@
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="n"/>
+          <t>554-03.905-06</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>20</v>
+      </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F33" s="26" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G33" s="26" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H33" s="26" t="n">
-        <v>6150</v>
+        <v>29055</v>
       </c>
       <c r="I33" s="26" t="n"/>
       <c r="J33" s="27" t="n"/>
@@ -2817,30 +2861,24 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>527-03.014</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="n">
-        <v>32</v>
-      </c>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr"/>
+      <c r="D34" s="24" t="n"/>
       <c r="E34" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="26" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>5600</v>
+        <v>27491</v>
       </c>
       <c r="I34" s="26" t="n"/>
       <c r="J34" s="27" t="n"/>
@@ -2856,14 +2894,10 @@
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>529-03.011</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый угловой Ду50</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr"/>
       <c r="D35" s="24" t="n">
         <v>50</v>
       </c>
@@ -2873,13 +2907,13 @@
         </is>
       </c>
       <c r="F35" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" s="26" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H35" s="26" t="n">
-        <v>5600</v>
+        <v>26820</v>
       </c>
       <c r="I35" s="26" t="n"/>
       <c r="J35" s="27" t="n"/>
@@ -2895,16 +2929,12 @@
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>595-01-010</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr"/>
       <c r="D36" s="24" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
@@ -2915,16 +2945,20 @@
         <v>2</v>
       </c>
       <c r="G36" s="26" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H36" s="26" t="n">
-        <v>5400</v>
-      </c>
-      <c r="I36" s="26" t="n"/>
-      <c r="J36" s="27" t="n"/>
+        <v>25330</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <v>19500</v>
+      </c>
+      <c r="J36" s="28" t="n">
+        <v>0.77</v>
+      </c>
       <c r="K36" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена ниже лома</t>
         </is>
       </c>
     </row>
@@ -2934,16 +2968,16 @@
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>без чертежа(527-35.1165)</t>
+          <t>529-03.003</t>
         </is>
       </c>
       <c r="D37" s="24" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
@@ -2954,10 +2988,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="26" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H37" s="26" t="n">
-        <v>4700</v>
+        <v>25107</v>
       </c>
       <c r="I37" s="26" t="n"/>
       <c r="J37" s="27" t="n"/>
@@ -2973,36 +3007,36 @@
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>(541-03.316-04)</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr"/>
       <c r="D38" s="24" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="26" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H38" s="26" t="n">
-        <v>893</v>
-      </c>
-      <c r="I38" s="26" t="n"/>
-      <c r="J38" s="27" t="n"/>
+        <v>23840</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <v>1.47</v>
+      </c>
       <c r="K38" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -3012,26 +3046,24 @@
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr"/>
-      <c r="D39" s="24" t="n">
-        <v>50</v>
-      </c>
+      <c r="D39" s="24" t="n"/>
       <c r="E39" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F39" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="26" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H39" s="26" t="n">
-        <v>4650</v>
+        <v>18327</v>
       </c>
       <c r="I39" s="26" t="n"/>
       <c r="J39" s="27" t="n"/>
@@ -3047,16 +3079,16 @@
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан фланцевый угловой Ду65 Ру40</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>595-3М-48</t>
+          <t>521-03.230</t>
         </is>
       </c>
       <c r="D40" s="24" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E40" s="24" t="inlineStr">
         <is>
@@ -3067,10 +3099,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H40" s="26" t="n">
-        <v>4650</v>
+        <v>14900</v>
       </c>
       <c r="I40" s="26" t="n"/>
       <c r="J40" s="27" t="n"/>
@@ -3086,16 +3118,16 @@
       </c>
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>595-35-021</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="D41" s="24" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
@@ -3106,10 +3138,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="26" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>4650</v>
+        <v>14155</v>
       </c>
       <c r="I41" s="26" t="n"/>
       <c r="J41" s="27" t="n"/>
@@ -3125,16 +3157,16 @@
       </c>
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>598-03.022-06</t>
+          <t>521-03.387</t>
         </is>
       </c>
       <c r="D42" s="24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
@@ -3142,13 +3174,13 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G42" s="26" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H42" s="26" t="n">
-        <v>4500</v>
+        <v>12814</v>
       </c>
       <c r="I42" s="26" t="n"/>
       <c r="J42" s="27" t="n"/>
@@ -3164,30 +3196,30 @@
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (верхние)</t>
+          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>(541-03.315-02)</t>
+          <t>521-35.2608-01</t>
         </is>
       </c>
       <c r="D43" s="24" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F43" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G43" s="26" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H43" s="26" t="n">
-        <v>826</v>
+        <v>12740</v>
       </c>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="27" t="n"/>
@@ -3203,16 +3235,12 @@
       </c>
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>521-35.2608-01</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr"/>
       <c r="D44" s="24" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
@@ -3220,19 +3248,23 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" s="26" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H44" s="26" t="n">
-        <v>3900</v>
-      </c>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="27" t="n"/>
+        <v>12665</v>
+      </c>
+      <c r="I44" s="26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J44" s="27" t="n">
+        <v>1.42</v>
+      </c>
       <c r="K44" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -3242,16 +3274,12 @@
       </c>
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>581-С6.73</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr"/>
       <c r="D45" s="24" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
@@ -3259,19 +3287,23 @@
         </is>
       </c>
       <c r="F45" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" s="26" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H45" s="26" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I45" s="26" t="n"/>
-      <c r="J45" s="27" t="n"/>
+        <v>12665</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>9750</v>
+      </c>
+      <c r="J45" s="28" t="n">
+        <v>0.77</v>
+      </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена ниже лома</t>
         </is>
       </c>
     </row>
@@ -3281,28 +3313,30 @@
       </c>
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="n"/>
+          <t>521-35.2754</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G46" s="26" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H46" s="26" t="n">
-        <v>3400</v>
+        <v>10281</v>
       </c>
       <c r="I46" s="26" t="n"/>
       <c r="J46" s="27" t="n"/>
@@ -3318,28 +3352,30 @@
       </c>
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="n"/>
+          <t>(541-03.232)</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="n">
+        <v>25</v>
+      </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="F47" s="26" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G47" s="26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H47" s="26" t="n">
-        <v>3400</v>
+        <v>8128</v>
       </c>
       <c r="I47" s="26" t="n"/>
       <c r="J47" s="27" t="n"/>
@@ -3355,12 +3391,12 @@
       </c>
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан с электромагнитным ручным управлением</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2619802505</t>
+          <t>587-182.126</t>
         </is>
       </c>
       <c r="D48" s="24" t="n"/>
@@ -3373,10 +3409,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H48" s="26" t="n">
-        <v>3400</v>
+        <v>9164</v>
       </c>
       <c r="I48" s="26" t="n"/>
       <c r="J48" s="27" t="n"/>
@@ -3392,16 +3428,16 @@
       </c>
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>595-03-006</t>
+          <t>522-01.497</t>
         </is>
       </c>
       <c r="D49" s="24" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
@@ -3409,19 +3445,23 @@
         </is>
       </c>
       <c r="F49" s="26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G49" s="26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H49" s="26" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I49" s="26" t="n"/>
-      <c r="J49" s="27" t="n"/>
+        <v>8672</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J49" s="27" t="n">
+        <v>1.15</v>
+      </c>
       <c r="K49" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3471,12 @@
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>595-03-006</t>
+          <t>527-03.014</t>
         </is>
       </c>
       <c r="D50" s="24" t="n">
@@ -3451,10 +3491,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H50" s="26" t="n">
-        <v>2800</v>
+        <v>8344</v>
       </c>
       <c r="I50" s="26" t="n"/>
       <c r="J50" s="27" t="n"/>
@@ -3470,16 +3510,16 @@
       </c>
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>521-3М.123</t>
+          <t>529-03.011</t>
         </is>
       </c>
       <c r="D51" s="24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
@@ -3490,10 +3530,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H51" s="26" t="n">
-        <v>2750</v>
+        <v>8344</v>
       </c>
       <c r="I51" s="26" t="n"/>
       <c r="J51" s="27" t="n"/>
@@ -3509,30 +3549,30 @@
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (нижние)</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>(541-03.316-02)</t>
+          <t>595-01-010</t>
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F52" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G52" s="26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H52" s="26" t="n">
-        <v>513</v>
+        <v>8046</v>
       </c>
       <c r="I52" s="26" t="n"/>
       <c r="J52" s="27" t="n"/>
@@ -3548,16 +3588,16 @@
       </c>
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>без чертежа(527-35.1165)</t>
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
@@ -3565,13 +3605,13 @@
         </is>
       </c>
       <c r="F53" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" s="26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H53" s="26" t="n">
-        <v>2550</v>
+        <v>7003</v>
       </c>
       <c r="I53" s="26" t="n"/>
       <c r="J53" s="27" t="n"/>
@@ -3587,30 +3627,30 @@
       </c>
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду25Ру100</t>
+          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>554-35.156</t>
+          <t>(541-03.316-04)</t>
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E54" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="F54" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G54" s="26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H54" s="26" t="n">
-        <v>2500</v>
+        <v>2444</v>
       </c>
       <c r="I54" s="26" t="n"/>
       <c r="J54" s="27" t="n"/>
@@ -3626,16 +3666,16 @@
       </c>
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
         <is>
-          <t>536-3М.72</t>
+          <t>521-01.471-01</t>
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
@@ -3643,19 +3683,23 @@
         </is>
       </c>
       <c r="F55" s="26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G55" s="26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H55" s="26" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I55" s="26" t="n"/>
-      <c r="J55" s="27" t="n"/>
+        <v>6937</v>
+      </c>
+      <c r="I55" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J55" s="27" t="n">
+        <v>1.15</v>
+      </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
-          <t>цены нет</t>
+          <t>цена почти как лом</t>
         </is>
       </c>
     </row>
@@ -3665,30 +3709,26 @@
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>541-03.224</t>
-        </is>
-      </c>
+          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr"/>
       <c r="D56" s="24" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F56" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56" s="26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H56" s="26" t="n">
-        <v>2250</v>
+        <v>6929</v>
       </c>
       <c r="I56" s="26" t="n"/>
       <c r="J56" s="27" t="n"/>
@@ -3704,16 +3744,16 @@
       </c>
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>524-03.188</t>
+          <t>595-3М-48</t>
         </is>
       </c>
       <c r="D57" s="24" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
@@ -3721,13 +3761,13 @@
         </is>
       </c>
       <c r="F57" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H57" s="26" t="n">
-        <v>2060</v>
+        <v>6929</v>
       </c>
       <c r="I57" s="26" t="n"/>
       <c r="J57" s="27" t="n"/>
@@ -3743,16 +3783,16 @@
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>536-35.696</t>
+          <t>595-35-021</t>
         </is>
       </c>
       <c r="D58" s="24" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
@@ -3763,10 +3803,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H58" s="26" t="n">
-        <v>2050</v>
+        <v>6929</v>
       </c>
       <c r="I58" s="26" t="n"/>
       <c r="J58" s="27" t="n"/>
@@ -3782,24 +3822,30 @@
       </c>
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="inlineStr"/>
-      <c r="D59" s="24" t="n"/>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>598-03.022-06</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F59" s="26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G59" s="26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H59" s="26" t="n">
-        <v>2000</v>
+        <v>6705</v>
       </c>
       <c r="I59" s="26" t="n"/>
       <c r="J59" s="27" t="n"/>
@@ -3815,40 +3861,36 @@
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Грибки АМГ Ду 150 (верхние)</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>521-03.124</t>
+          <t>(541-03.315-02)</t>
         </is>
       </c>
       <c r="D60" s="24" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E60" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="F60" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H60" s="26" t="n">
-        <v>1750</v>
-      </c>
-      <c r="I60" s="26" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J60" s="27" t="n">
-        <v>1.43</v>
-      </c>
+        <v>2262</v>
+      </c>
+      <c r="I60" s="26" t="n"/>
+      <c r="J60" s="27" t="n"/>
       <c r="K60" s="24" t="inlineStr">
         <is>
-          <t>цена почти как лом</t>
+          <t>цены нет</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3900,16 @@
       </c>
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="inlineStr"/>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>521-35.2608-01</t>
+        </is>
+      </c>
       <c r="D61" s="24" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
@@ -3871,23 +3917,19 @@
         </is>
       </c>
       <c r="F61" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" s="26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H61" s="26" t="n">
-        <v>1650</v>
-      </c>
-      <c r="I61" s="26" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J61" s="28" t="n">
-        <v>0.91</v>
-      </c>
+        <v>5811</v>
+      </c>
+      <c r="I61" s="26" t="n"/>
+      <c r="J61" s="27" t="n"/>
       <c r="K61" s="24" t="inlineStr">
         <is>
-          <t>цена ниже лома</t>
+          <t>цены нет</t>
         </is>
       </c>
     </row>
@@ -3897,16 +3939,16 @@
       </c>
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>554-35.265</t>
+          <t>581-С6.73</t>
         </is>
       </c>
       <c r="D62" s="24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E62" s="24" t="inlineStr">
         <is>
@@ -3914,13 +3956,13 @@
         </is>
       </c>
       <c r="F62" s="26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G62" s="26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H62" s="26" t="n">
-        <v>1500</v>
+        <v>5364</v>
       </c>
       <c r="I62" s="26" t="n"/>
       <c r="J62" s="27" t="n"/>
@@ -3936,17 +3978,15 @@
       </c>
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>528-35.176</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="n">
-        <v>15</v>
-      </c>
+          <t>2619802505</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="n"/>
       <c r="E63" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -3956,10 +3996,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H63" s="26" t="n">
-        <v>1300</v>
+        <v>5066</v>
       </c>
       <c r="I63" s="26" t="n"/>
       <c r="J63" s="27" t="n"/>
@@ -3975,17 +4015,15 @@
       </c>
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>521-01.493-02</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="n">
-        <v>10</v>
-      </c>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="n"/>
       <c r="E64" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -3995,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H64" s="26" t="n">
-        <v>1164</v>
+        <v>5066</v>
       </c>
       <c r="I64" s="26" t="n"/>
       <c r="J64" s="27" t="n"/>
@@ -4014,17 +4052,15 @@
       </c>
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>522-03.089</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="n">
-        <v>20</v>
-      </c>
+          <t>2619802505</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="n"/>
       <c r="E65" s="24" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -4034,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H65" s="26" t="n">
-        <v>1150</v>
+        <v>5066</v>
       </c>
       <c r="I65" s="26" t="n"/>
       <c r="J65" s="27" t="n"/>
@@ -4053,16 +4089,16 @@
       </c>
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>521-03.406</t>
+          <t>595-03-006</t>
         </is>
       </c>
       <c r="D66" s="24" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E66" s="24" t="inlineStr">
         <is>
@@ -4070,13 +4106,13 @@
         </is>
       </c>
       <c r="F66" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" s="26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H66" s="26" t="n">
-        <v>1100</v>
+        <v>4321</v>
       </c>
       <c r="I66" s="26" t="n"/>
       <c r="J66" s="27" t="n"/>
@@ -4092,12 +4128,16 @@
       </c>
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
-        </is>
-      </c>
-      <c r="C67" s="24" t="inlineStr"/>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>595-03-006</t>
+        </is>
+      </c>
       <c r="D67" s="24" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
@@ -4108,20 +4148,16 @@
         <v>1</v>
       </c>
       <c r="G67" s="26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H67" s="26" t="n">
-        <v>975</v>
-      </c>
-      <c r="I67" s="26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J67" s="27" t="n">
-        <v>1.03</v>
-      </c>
+        <v>4172</v>
+      </c>
+      <c r="I67" s="26" t="n"/>
+      <c r="J67" s="27" t="n"/>
       <c r="K67" s="24" t="inlineStr">
         <is>
-          <t>цена почти как лом</t>
+          <t>цены нет</t>
         </is>
       </c>
     </row>
@@ -4131,16 +4167,16 @@
       </c>
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>524-03.004</t>
+          <t>521-3М.123</t>
         </is>
       </c>
       <c r="D68" s="24" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
@@ -4151,10 +4187,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H68" s="26" t="n">
-        <v>760</v>
+        <v>4098</v>
       </c>
       <c r="I68" s="26" t="n"/>
       <c r="J68" s="27" t="n"/>
@@ -4170,28 +4206,30 @@
       </c>
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
+          <t>Грибки АМГ Ду 150 (нижние)</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>525-35.577</t>
-        </is>
-      </c>
-      <c r="D69" s="24" t="n"/>
+          <t>(541-03.316-02)</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="n">
+        <v>150</v>
+      </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="F69" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H69" s="26" t="n">
-        <v>633</v>
+        <v>1404</v>
       </c>
       <c r="I69" s="26" t="n"/>
       <c r="J69" s="27" t="n"/>
@@ -4207,32 +4245,949 @@
       </c>
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>521-03.472-01</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="n"/>
+          <t>554-03.909-03</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="n">
+        <v>20</v>
+      </c>
       <c r="E70" s="24" t="inlineStr">
         <is>
-          <t>нержавейка</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H70" s="26" t="n">
-        <v>32</v>
+        <v>3799</v>
       </c>
       <c r="I70" s="26" t="n"/>
       <c r="J70" s="27" t="n"/>
       <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду25Ру100</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>554-35.156</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F71" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="26" t="n">
+        <v>3725</v>
+      </c>
+      <c r="I71" s="26" t="n"/>
+      <c r="J71" s="27" t="n"/>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>536-3М.72</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F72" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H72" s="26" t="n">
+        <v>3725</v>
+      </c>
+      <c r="I72" s="26" t="n"/>
+      <c r="J72" s="27" t="n"/>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>521-01.469-02</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" s="26" t="n">
+        <v>3469</v>
+      </c>
+      <c r="I73" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J73" s="27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>цена почти как лом</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>541-03.224</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>латунь</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="26" t="n">
+        <v>2858</v>
+      </c>
+      <c r="I74" s="26" t="n"/>
+      <c r="J74" s="27" t="n"/>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>524-03.188</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F75" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" s="26" t="n">
+        <v>3069</v>
+      </c>
+      <c r="I75" s="26" t="n"/>
+      <c r="J75" s="27" t="n"/>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>536-35.696</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F76" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="26" t="n">
+        <v>3054</v>
+      </c>
+      <c r="I76" s="26" t="n"/>
+      <c r="J76" s="27" t="n"/>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr"/>
+      <c r="D77" s="24" t="n"/>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" s="26" t="n">
+        <v>2980</v>
+      </c>
+      <c r="I77" s="26" t="n"/>
+      <c r="J77" s="27" t="n"/>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>521-03.124</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="26" t="n">
+        <v>2608</v>
+      </c>
+      <c r="I78" s="26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J78" s="28" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K78" s="24" t="inlineStr">
+        <is>
+          <t>цена ниже лома</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr"/>
+      <c r="D79" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" s="26" t="n">
+        <v>2458</v>
+      </c>
+      <c r="I79" s="26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J79" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>цена ниже лома</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>554-35.265</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" s="26" t="n">
+        <v>2235</v>
+      </c>
+      <c r="I80" s="26" t="n"/>
+      <c r="J80" s="27" t="n"/>
+      <c r="K80" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>528-35.176</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H81" s="26" t="n">
+        <v>1937</v>
+      </c>
+      <c r="I81" s="26" t="n"/>
+      <c r="J81" s="27" t="n"/>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>521-3м-52</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="26" t="n">
+        <v>1734</v>
+      </c>
+      <c r="I82" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J82" s="27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>цена почти как лом</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>522-01.499-01</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" s="26" t="n">
+        <v>1734</v>
+      </c>
+      <c r="I83" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J83" s="27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>цена почти как лом</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>521-01.467-03</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" s="26" t="n">
+        <v>1734</v>
+      </c>
+      <c r="I84" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J84" s="27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>цена почти как лом</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>Без чертежа</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F85" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" s="26" t="n">
+        <v>1734</v>
+      </c>
+      <c r="I85" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J85" s="27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>цена почти как лом</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>521-01.469-02</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" s="26" t="n">
+        <v>1734</v>
+      </c>
+      <c r="I86" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J86" s="27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>цена почти как лом</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>521-01.493-02</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F87" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" s="26" t="n">
+        <v>1734</v>
+      </c>
+      <c r="I87" s="26" t="n"/>
+      <c r="J87" s="27" t="n"/>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>522-03.089</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" s="26" t="n">
+        <v>1713</v>
+      </c>
+      <c r="I88" s="26" t="n"/>
+      <c r="J88" s="27" t="n"/>
+      <c r="K88" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>521-03.406</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F89" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" s="26" t="n">
+        <v>1639</v>
+      </c>
+      <c r="I89" s="26" t="n"/>
+      <c r="J89" s="27" t="n"/>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr"/>
+      <c r="D90" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="26" t="n">
+        <v>1453</v>
+      </c>
+      <c r="I90" s="26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J90" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K90" s="24" t="inlineStr">
+        <is>
+          <t>цена ниже лома</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>524-03.004</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F91" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" s="26" t="n">
+        <v>1132</v>
+      </c>
+      <c r="I91" s="26" t="n"/>
+      <c r="J91" s="27" t="n"/>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>Клапан дроссельный угловой штуцерный</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>525-35.577</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="n"/>
+      <c r="E92" s="24" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="26" t="n">
+        <v>942</v>
+      </c>
+      <c r="I92" s="26" t="n"/>
+      <c r="J92" s="27" t="n"/>
+      <c r="K92" s="24" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="25" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>521-03.472-01</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="n"/>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>нержавейка</t>
+        </is>
+      </c>
+      <c r="F93" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="I93" s="26" t="n"/>
+      <c r="J93" s="27" t="n"/>
+      <c r="K93" s="24" t="inlineStr">
         <is>
           <t>цены нет</t>
         </is>

--- a/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
+++ b/outputs/marine_equipment/Сравнение_лом_и_продажа.xlsx
@@ -879,7 +879,7 @@
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>— Лом считаем по бронзе 745 руб за кг. Если часть окажется латунью по 635, лом просядет до 17.3 млн. Это еще один довод проставить материал в учете.</t>
+          <t>— Лом считаем по бронзе 745 руб за кг. Если часть окажется латунью по 635, лом просядет до 0.0 млн. Это еще один довод проставить материал в учете.</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F5" s="26" t="n">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F6" s="26" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F7" s="26" t="n">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F8" s="26" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F9" s="26" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F10" s="26" t="n">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F12" s="26" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F13" s="26" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F14" s="26" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F15" s="26" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F17" s="26" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F18" s="26" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F19" s="26" t="n">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F20" s="26" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F22" s="26" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F23" s="26" t="n">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F24" s="26" t="n">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F25" s="26" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F26" s="26" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F27" s="26" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F28" s="26" t="n">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F29" s="26" t="n">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F30" s="26" t="n">
@@ -2792,7 +2792,7 @@
       <c r="D32" s="24" t="n"/>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F32" s="26" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F33" s="26" t="n">
@@ -2868,7 +2868,7 @@
       <c r="D34" s="24" t="n"/>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F34" s="26" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F35" s="26" t="n">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F36" s="26" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F37" s="26" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F38" s="26" t="n">
@@ -3053,7 +3053,7 @@
       <c r="D39" s="24" t="n"/>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F39" s="26" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F40" s="26" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F41" s="26" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F42" s="26" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F43" s="26" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F44" s="26" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F45" s="26" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F46" s="26" t="n">
@@ -3402,7 +3402,7 @@
       <c r="D48" s="24" t="n"/>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F48" s="26" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F49" s="26" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F50" s="26" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F51" s="26" t="n">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F52" s="26" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F53" s="26" t="n">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F55" s="26" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F56" s="26" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F57" s="26" t="n">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F58" s="26" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F59" s="26" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F61" s="26" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="E62" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F62" s="26" t="n">
@@ -3989,7 +3989,7 @@
       <c r="D63" s="24" t="n"/>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F63" s="26" t="n">
@@ -4026,7 +4026,7 @@
       <c r="D64" s="24" t="n"/>
       <c r="E64" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F64" s="26" t="n">
@@ -4063,7 +4063,7 @@
       <c r="D65" s="24" t="n"/>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F65" s="26" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E66" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F66" s="26" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F67" s="26" t="n">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F68" s="26" t="n">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E70" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F70" s="26" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F71" s="26" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F72" s="26" t="n">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F73" s="26" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F75" s="26" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F76" s="26" t="n">
@@ -4529,7 +4529,7 @@
       <c r="D77" s="24" t="n"/>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F77" s="26" t="n">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="E78" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F78" s="26" t="n">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F79" s="26" t="n">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="E80" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F80" s="26" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F81" s="26" t="n">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="E82" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F82" s="26" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F83" s="26" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E84" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F84" s="26" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F85" s="26" t="n">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="E86" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F86" s="26" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F87" s="26" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="E88" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F88" s="26" t="n">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F89" s="26" t="n">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E90" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F90" s="26" t="n">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F91" s="26" t="n">
@@ -5136,7 +5136,7 @@
       <c r="D92" s="24" t="n"/>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="F92" s="26" t="n">
